--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513085_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513085_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5102</v>
+        <v>2.0633</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4471</v>
+        <v>1.4903</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9369</v>
+        <v>0.5729</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7821</v>
+        <v>0.1194</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6865</v>
+        <v>0.118</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.4686</v>
+        <v>0.0014</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7651</v>
+        <v>1.3522</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3038</v>
+        <v>0.8679</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5387</v>
+        <v>0.4843</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5473</v>
+        <v>-1.2327</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6173</v>
+        <v>-0.7499</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9299</v>
+        <v>-0.4829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.4172</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.8221</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9198</v>
+        <v>0.8119</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7062</v>
+        <v>0.7093</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2137</v>
+        <v>0.1027</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2421</v>
+        <v>0.727</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2421</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3037</v>
+        <v>1.9278</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7435</v>
+        <v>5.1338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5602</v>
+        <v>-3.206</v>
       </c>
       <c r="G3" t="n">
-        <v>0.104</v>
+        <v>-0.5894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1061</v>
+        <v>-1.6993</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0021</v>
+        <v>1.1099</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2949</v>
+        <v>3.5169</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8312</v>
+        <v>0.1956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4637</v>
+        <v>3.3214</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1909</v>
+        <v>-4.1064</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7251</v>
+        <v>-1.8949</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4658</v>
+        <v>-2.2115</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4097</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4339</v>
+        <v>-3.0368</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8436</v>
+        <v>1.4172</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0757</v>
+        <v>0.1834</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0501</v>
+        <v>0.3302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0255</v>
+        <v>-0.1469</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7143</v>
+        <v>3.9534</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8324</v>
+        <v>4.3234</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1181</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2364</v>
+        <v>1.0475</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2147</v>
+        <v>3.2933</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4511</v>
+        <v>-2.2458</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9906</v>
+        <v>-0.7861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8471</v>
+        <v>1.6993</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1435</v>
+        <v>-2.4854</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8616</v>
+        <v>2.8246</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6245000000000001</v>
+        <v>3.3577</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2371</v>
+        <v>-0.5331</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1291</v>
+        <v>-3.6107</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2226</v>
+        <v>-1.6584</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0935</v>
+        <v>-1.9523</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8194</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4339</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6145</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7288</v>
+        <v>1.4772</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1156</v>
+        <v>1.4809</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6132</v>
+        <v>-0.0037</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3364</v>
+        <v>-0.2509</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7628</v>
+        <v>1.4701</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9669</v>
+        <v>-0.5079</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.624</v>
+        <v>0.4031</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6865</v>
+        <v>-0.3169</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0625</v>
+        <v>0.7199</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4023</v>
+        <v>0.984</v>
       </c>
       <c r="K5" t="n">
-        <v>0.154</v>
+        <v>-0.7724</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2483</v>
+        <v>1.7565</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.0262</v>
+        <v>-0.581</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8405</v>
+        <v>0.4556</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1857</v>
+        <v>-1.0365</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8492</v>
+        <v>0.5831</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8348</v>
+        <v>0.4861</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0144</v>
+        <v>0.097</v>
       </c>
       <c r="V5" t="n">
-        <v>3.9079</v>
+        <v>-1.4411</v>
       </c>
       <c r="W5" t="n">
-        <v>4.268</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3601</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5698</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.238</v>
+        <v>-0.377</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6682</v>
+        <v>1.0711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3763</v>
+        <v>0.9666</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3287</v>
+        <v>0.831</v>
       </c>
       <c r="I6" t="n">
-        <v>0.705</v>
+        <v>0.1355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8707</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8023</v>
+        <v>0.6322</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7282</v>
+        <v>0.2385</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5496</v>
+        <v>0.0959</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4736</v>
+        <v>0.1989</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0232</v>
+        <v>-0.103</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4339</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.4172</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1823</v>
+        <v>0.2189</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3121</v>
+        <v>-0.0815</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1299</v>
+        <v>0.3004</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4227</v>
+        <v>0.3184</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4227</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4657</v>
+        <v>0.1811</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1834</v>
+        <v>3.1936</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7177</v>
+        <v>-3.0125</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3798</v>
+        <v>-1.4034</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4854</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8943</v>
+        <v>-0.8909</v>
       </c>
       <c r="J7" t="n">
-        <v>2.502</v>
+        <v>2.5432</v>
       </c>
       <c r="K7" t="n">
-        <v>1.327</v>
+        <v>1.3433</v>
       </c>
       <c r="L7" t="n">
-        <v>1.175</v>
+        <v>1.1999</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8818</v>
+        <v>-3.9467</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8125</v>
+        <v>-1.8559</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0693</v>
+        <v>-2.0908</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8212</v>
+        <v>0.5723</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6814</v>
+        <v>0.6504</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1398</v>
+        <v>-0.0781</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1834</v>
+        <v>-0.3662</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.157</v>
+        <v>-0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0265</v>
+        <v>-0.0062</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7688</v>
+        <v>-0.7706</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1116</v>
+        <v>-0.1183</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1116</v>
+        <v>-0.1183</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1116</v>
+        <v>-0.1183</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3806</v>
+        <v>0.202</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5003</v>
+        <v>0.2924</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1197</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6012</v>
+        <v>-0.3683</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7549</v>
+        <v>-1.7023</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1536</v>
+        <v>1.334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.016</v>
+        <v>-0.0032</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1089</v>
+        <v>-0.1181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1248</v>
+        <v>0.1149</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5592</v>
+        <v>-0.5533</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6382</v>
+        <v>-0.6328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5752</v>
+        <v>0.5501</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5294</v>
+        <v>0.5147</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0346</v>
+        <v>0.2907</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2383</v>
+        <v>0.2681</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2037</v>
+        <v>0.0226</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1442</v>
+        <v>-2.3479</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3591</v>
+        <v>-2.5698</v>
       </c>
       <c r="F10" t="n">
-        <v>0.215</v>
+        <v>0.2219</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3964</v>
+        <v>-2.3905</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5827</v>
+        <v>-0.5925</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8137</v>
+        <v>-1.798</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7535</v>
+        <v>-2.7254</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6382</v>
+        <v>-0.6328</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1153</v>
+        <v>-2.0925</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3571</v>
+        <v>0.3349</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0555</v>
+        <v>0.0403</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3016</v>
+        <v>0.2945</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8183</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.804</v>
+        <v>0.5605</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0142</v>
+        <v>0.065</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.117</v>
+        <v>-2.408</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1566</v>
+        <v>-2.5724</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0397</v>
+        <v>0.1644</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1627</v>
+        <v>-1.1537</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8427</v>
+        <v>-1.8574</v>
       </c>
       <c r="I11" t="n">
-        <v>0.68</v>
+        <v>0.7037</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.544</v>
+        <v>-0.5008</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0618</v>
+        <v>-1.0483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5177</v>
+        <v>0.5476</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6186</v>
+        <v>-0.6529</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7809</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1623</v>
+        <v>0.1561</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3732</v>
+        <v>-0.7034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7205</v>
+        <v>-0.2251</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.4783</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8771</v>
+        <v>1.8785</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1439</v>
+        <v>-3.7522</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8738</v>
+        <v>-4.6887</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7299</v>
+        <v>0.9366</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7445</v>
+        <v>-1.7247</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0973</v>
+        <v>-0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6472</v>
+        <v>-1.6448</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7935</v>
+        <v>-2.7492</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8218</v>
+        <v>-0.7922</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9717</v>
+        <v>-1.957</v>
       </c>
       <c r="M12" t="n">
-        <v>1.049</v>
+        <v>1.0245</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7245</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0054</v>
+        <v>0.375</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0501</v>
+        <v>0.1659</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0447</v>
+        <v>0.2091</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9952</v>
+        <v>-1.9975</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9761</v>
+        <v>-6.2996</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2805</v>
+        <v>-3.2245</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6956</v>
+        <v>-3.0751</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.9588</v>
+        <v>-6.9875</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5537</v>
+        <v>-2.5878</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.405</v>
+        <v>-4.3998</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7738</v>
+        <v>-3.733</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1593</v>
+        <v>-1.1471</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6145</v>
+        <v>-2.5858</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.185</v>
+        <v>-3.2546</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3944</v>
+        <v>-1.4406</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7906</v>
+        <v>-1.8139</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8474</v>
+        <v>0.58</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4933</v>
+        <v>0.5084</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3541</v>
+        <v>0.0716</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.2841</v>
+        <v>-8.6662</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.421799999999999</v>
+        <v>-0.9136000000000006</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.862300000000001</v>
+        <v>-7.7526</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.3302</v>
+        <v>-14.32</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.1578</v>
+        <v>-5.2346</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.1723</v>
+        <v>-9.085899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6705999999999981</v>
+        <v>1.1776</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1189</v>
+        <v>1.3711</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4483999999999999</v>
+        <v>-0.1930000000000005</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.0006</v>
+        <v>-15.4979</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.2767</v>
+        <v>-6.6053</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.723800000000001</v>
+        <v>-8.8927</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.000300000000000189</v>
+        <v>0.000300000000000411</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.3149</v>
+        <v>-13.1596</v>
       </c>
       <c r="R14" t="n">
-        <v>13.3147</v>
+        <v>13.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5917</v>
+        <v>5.216599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3961</v>
+        <v>5.145599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1954</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4542999999999997</v>
+        <v>0.4374999999999993</v>
       </c>
       <c r="W14" t="n">
-        <v>5.826599999999999</v>
+        <v>5.9222</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3723</v>
+        <v>-5.4848</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9561</v>
+        <v>6.7667</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4193</v>
+        <v>5.4344</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5368</v>
+        <v>1.3323</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7091</v>
+        <v>2.6869</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3568</v>
+        <v>0.3559</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3524</v>
+        <v>2.3311</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3594</v>
+        <v>2.4244</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3296</v>
+        <v>0.3733</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0298</v>
+        <v>2.051</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3497</v>
+        <v>0.2626</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0272</v>
+        <v>-0.0175</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3226</v>
+        <v>0.2801</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2371</v>
+        <v>-0.4221</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2146</v>
+        <v>0.1278</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4517</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8453</v>
+        <v>2.8823</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8453</v>
+        <v>2.8823</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3575</v>
+        <v>6.5155</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2635</v>
+        <v>7.3794</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.906</v>
+        <v>-0.8638</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7154</v>
+        <v>7.7733</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9132</v>
+        <v>2.9438</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8021</v>
+        <v>4.8295</v>
       </c>
       <c r="J16" t="n">
-        <v>8.9214</v>
+        <v>9.051</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5828</v>
+        <v>3.6533</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3386</v>
+        <v>5.3977</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.206</v>
+        <v>-1.2777</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6696</v>
+        <v>-0.7096</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5364</v>
+        <v>-0.5682</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.153</v>
+        <v>-0.0553</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8515</v>
+        <v>0.1019</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3015</v>
+        <v>-0.1572</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4678</v>
+        <v>4.0434</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9758</v>
+        <v>2.3238</v>
       </c>
       <c r="F17" t="n">
-        <v>1.492</v>
+        <v>1.7196</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4876</v>
+        <v>5.4834</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0933</v>
+        <v>2.0952</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3943</v>
+        <v>3.3882</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1092</v>
+        <v>4.1442</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6198</v>
+        <v>1.6397</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4895</v>
+        <v>2.5046</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3784</v>
+        <v>1.3392</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4736</v>
+        <v>0.4556</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9048</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4424</v>
+        <v>-0.8811</v>
       </c>
       <c r="T17" t="n">
-        <v>0.673</v>
+        <v>-0.0469</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1155</v>
+        <v>-0.8343</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6143</v>
+        <v>0.6379</v>
       </c>
       <c r="E18" t="n">
-        <v>0.33</v>
+        <v>-2.4635</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2842</v>
+        <v>3.1014</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1159</v>
+        <v>-0.1227</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9344</v>
+        <v>-0.5337</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1814</v>
+        <v>0.4109</v>
       </c>
       <c r="J18" t="n">
-        <v>3.23</v>
+        <v>-0.887</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4647</v>
+        <v>-0.2581</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7653</v>
+        <v>-0.6288</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1141</v>
+        <v>0.7642</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5302</v>
+        <v>-0.2755</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4161</v>
+        <v>1.0397</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9113</v>
+        <v>0.4772</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8515</v>
+        <v>0.448</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0598</v>
+        <v>0.0292</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1806</v>
+        <v>0.6883</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1806</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5997</v>
+        <v>0.4672</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4303</v>
+        <v>0.8454</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0301</v>
+        <v>-0.3782</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1081</v>
+        <v>3.099</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5324</v>
+        <v>1.9371</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4243</v>
+        <v>1.1619</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9239000000000001</v>
+        <v>3.2871</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2812</v>
+        <v>2.5082</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6427</v>
+        <v>0.7788</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8158</v>
+        <v>-0.1881</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2512</v>
+        <v>-0.5712</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0671</v>
+        <v>0.3831</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S19" t="n">
-        <v>0.421</v>
+        <v>-1.0367</v>
       </c>
       <c r="T19" t="n">
-        <v>0.542</v>
+        <v>-0.4172</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.121</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6965</v>
+        <v>-1.1902</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6965</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="20">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2544</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0785</v>
+        <v>0.0793</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3329</v>
+        <v>-0.1454</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4031</v>
+        <v>0.3915</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4571</v>
+        <v>0.4548</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.054</v>
+        <v>-0.0633</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0785</v>
+        <v>0.0793</v>
       </c>
       <c r="K20" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4181</v>
+        <v>0.4153</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0935</v>
+        <v>-0.103</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6575</v>
+        <v>-0.4576</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6575</v>
+        <v>-0.4576</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5401</v>
+        <v>-0.1852</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6294</v>
+        <v>-2.1937</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0893</v>
+        <v>2.0086</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.799</v>
+        <v>-1.881</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9254</v>
+        <v>-1.9371</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9332</v>
+        <v>-1.6551</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6187</v>
+        <v>-0.9305</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3145</v>
+        <v>-0.7246</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1342</v>
+        <v>-0.226</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3068</v>
+        <v>-1.0066</v>
       </c>
       <c r="O21" t="n">
-        <v>0.441</v>
+        <v>0.7806</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2291</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>2.227</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0298</v>
+        <v>0.3032</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3038</v>
+        <v>0.2956</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.274</v>
+        <v>0.0076</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6446</v>
+        <v>-0.7486</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.293</v>
+        <v>-1.9213</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6484</v>
+        <v>1.1727</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8699</v>
+        <v>-1.8006</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9344</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0645</v>
+        <v>-0.8717</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7052</v>
+        <v>-1.9177</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9584</v>
+        <v>-0.6131</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7468</v>
+        <v>-1.3047</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1648</v>
+        <v>0.1171</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.976</v>
+        <v>-0.3158</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8113</v>
+        <v>0.433</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>1.2147</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2533</v>
+        <v>1.2147</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1601</v>
+        <v>-0.1627</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2801</v>
+        <v>-0.0035</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4402</v>
+        <v>-0.1591</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4878</v>
+        <v>-2.7549</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7177</v>
+        <v>-0.191</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7701</v>
+        <v>-2.5639</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2621</v>
+        <v>-1.2709</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6132</v>
+        <v>-0.6128</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6489</v>
+        <v>-0.6581</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5073</v>
+        <v>-0.4687</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1145</v>
+        <v>-1.0885</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6072</v>
+        <v>0.6198</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7548</v>
+        <v>-0.8022</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5013</v>
+        <v>0.4757</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2561</v>
+        <v>-1.278</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7174</v>
+        <v>-0.9699</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1135</v>
+        <v>-0.6733</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6039</v>
+        <v>-0.2966</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8453</v>
+        <v>-2.8823</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7844</v>
+        <v>-3.9372</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1345</v>
+        <v>-1.5401</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6499</v>
+        <v>-2.3971</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0619</v>
+        <v>-0.0386</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4084</v>
+        <v>1.4601</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4703</v>
+        <v>-1.4988</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3716</v>
+        <v>1.4404</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2136</v>
+        <v>1.2814</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1581</v>
+        <v>0.159</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4335</v>
+        <v>-1.4791</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1949</v>
+        <v>0.1787</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6283</v>
+        <v>-1.6578</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2365</v>
+        <v>0.061</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6075</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3711</v>
+        <v>-0.0358</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.7542</v>
+        <v>-3.7571</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.0895</v>
+        <v>-2.065</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.2841</v>
+        <v>10.7387</v>
       </c>
       <c r="E25" t="n">
-        <v>6.8622</v>
+        <v>7.7527</v>
       </c>
       <c r="F25" t="n">
-        <v>2.421900000000001</v>
+        <v>2.9862</v>
       </c>
       <c r="G25" t="n">
-        <v>14.3301</v>
+        <v>14.3203</v>
       </c>
       <c r="H25" t="n">
-        <v>5.157800000000001</v>
+        <v>5.2344</v>
       </c>
       <c r="I25" t="n">
-        <v>9.1723</v>
+        <v>9.085700000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>15.0005</v>
+        <v>15.4979</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2767</v>
+        <v>6.6052</v>
       </c>
       <c r="L25" t="n">
-        <v>8.723999999999998</v>
+        <v>8.892600000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6706</v>
+        <v>-1.177800000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1187</v>
+        <v>-1.3709</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4485999999999997</v>
+        <v>0.1931000000000003</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0001000000000000723</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.3152</v>
+        <v>-13.1593</v>
       </c>
       <c r="R25" t="n">
-        <v>13.3151</v>
+        <v>13.1594</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.5915</v>
+        <v>-3.144</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1954999999999998</v>
+        <v>-0.07089999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.3962</v>
+        <v>-3.0732</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4544000000000001</v>
+        <v>-0.4375</v>
       </c>
       <c r="W25" t="n">
-        <v>5.372100000000001</v>
+        <v>5.4848</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.826499999999999</v>
+        <v>-5.9223</v>
       </c>
     </row>
   </sheetData>
